--- a/doc/分工表.xlsx
+++ b/doc/分工表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms169\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms169\Desktop\Tuozhu-Software\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4532ECC8-54BC-43BC-9AA1-4D6C8247A4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BC50D4-D5C5-41EC-BE96-334DB1162073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{82B2D615-F6D9-4577-86AD-1DF889E5A29C}"/>
   </bookViews>
@@ -481,34 +481,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -859,35 +859,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5"/>
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
       <c r="C1" s="12"/>
       <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
       <c r="G1" s="12"/>
       <c r="H1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
       <c r="K1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="27.85" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -896,10 +896,10 @@
       <c r="F2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="7">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -908,77 +908,77 @@
       <c r="J2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9"/>
       <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3"/>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10"/>
       <c r="I3" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
+      <c r="A4" s="9"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9"/>
       <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3"/>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10"/>
       <c r="I4" s="1" t="s">
         <v>44</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2"/>
+      <c r="A5" s="9"/>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -987,335 +987,338 @@
       <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3"/>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10"/>
       <c r="I5" s="1" t="s">
         <v>45</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="2"/>
+      <c r="A6" s="9"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9"/>
       <c r="E6" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3"/>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10"/>
       <c r="I6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2"/>
+      <c r="A7" s="9"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9"/>
       <c r="E7" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3"/>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10"/>
       <c r="I7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2"/>
+      <c r="A8" s="9"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9"/>
       <c r="E8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3"/>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10"/>
       <c r="I8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="7">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3"/>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10"/>
       <c r="I9" s="1" t="s">
         <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3"/>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10"/>
       <c r="I10" s="1" t="s">
         <v>50</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="7">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
       <c r="F11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3"/>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10"/>
       <c r="I11" s="1" t="s">
         <v>51</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="7">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
       <c r="F12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3"/>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10"/>
       <c r="I12" s="1" t="s">
         <v>52</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="7">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="7">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3"/>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10"/>
       <c r="I13" s="1" t="s">
         <v>53</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="7">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3"/>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10"/>
       <c r="I14" s="1" t="s">
         <v>54</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="27.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="8">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="7">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="6" t="s">
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="27.85" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="10">
+      <c r="B16" s="7"/>
+      <c r="C16" s="6">
         <f>AVERAGE(C2:C15)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="11" t="s">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10">
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="6">
         <f>AVERAGE(G2:G15)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="10">
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="6">
         <f>AVERAGE(K2:K15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="8:8" ht="27.85" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="H17" s="4"/>
+      <c r="H17" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:K1"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="H16:J16"/>
@@ -1327,9 +1330,6 @@
     <mergeCell ref="A2:A8"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="D9:D14"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="H1:K1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C2:C16 G2:G16 K2:K16">

--- a/doc/分工表.xlsx
+++ b/doc/分工表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms169\Desktop\Tuozhu-Software\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BC50D4-D5C5-41EC-BE96-334DB1162073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD2857A-FE12-4A33-ACFE-FEB611D076CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{82B2D615-F6D9-4577-86AD-1DF889E5A29C}"/>
   </bookViews>
@@ -496,6 +496,15 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -506,15 +515,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -859,26 +859,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13" t="s">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13" t="s">
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="12"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" ht="27.85" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -887,7 +887,7 @@
       <c r="C2" s="4">
         <v>1</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -899,7 +899,7 @@
       <c r="G2" s="4">
         <v>0</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -913,14 +913,14 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9"/>
+      <c r="A3" s="12"/>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
@@ -930,7 +930,7 @@
       <c r="G3" s="4">
         <v>0</v>
       </c>
-      <c r="H3" s="10"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="1" t="s">
         <v>43</v>
       </c>
@@ -942,14 +942,14 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9"/>
+      <c r="A4" s="12"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="D4" s="12"/>
       <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
@@ -959,7 +959,7 @@
       <c r="G4" s="4">
         <v>0</v>
       </c>
-      <c r="H4" s="10"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="1" t="s">
         <v>44</v>
       </c>
@@ -971,14 +971,14 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="9"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -990,7 +990,7 @@
       <c r="G5" s="4">
         <v>0</v>
       </c>
-      <c r="H5" s="10"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="1" t="s">
         <v>45</v>
       </c>
@@ -1002,14 +1002,14 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="9"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="1" t="s">
         <v>41</v>
       </c>
@@ -1019,7 +1019,7 @@
       <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="H6" s="10"/>
+      <c r="H6" s="13"/>
       <c r="I6" s="1" t="s">
         <v>46</v>
       </c>
@@ -1031,14 +1031,14 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="D7" s="12"/>
       <c r="E7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1048,7 +1048,7 @@
       <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="10"/>
+      <c r="H7" s="13"/>
       <c r="I7" s="1" t="s">
         <v>47</v>
       </c>
@@ -1060,14 +1060,14 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="9"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="D8" s="12"/>
       <c r="E8" s="1" t="s">
         <v>29</v>
       </c>
@@ -1077,7 +1077,7 @@
       <c r="G8" s="4">
         <v>0</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="13"/>
       <c r="I8" s="1" t="s">
         <v>48</v>
       </c>
@@ -1089,7 +1089,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1098,10 +1098,10 @@
       <c r="C9" s="4">
         <v>0</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="12" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -1110,7 +1110,7 @@
       <c r="G9" s="4">
         <v>0</v>
       </c>
-      <c r="H9" s="10"/>
+      <c r="H9" s="13"/>
       <c r="I9" s="1" t="s">
         <v>49</v>
       </c>
@@ -1122,22 +1122,22 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="10"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
-      <c r="H10" s="10"/>
+      <c r="H10" s="13"/>
       <c r="I10" s="1" t="s">
         <v>50</v>
       </c>
@@ -1149,22 +1149,22 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="10"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="4">
         <v>0</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
       <c r="F11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
-      <c r="H11" s="10"/>
+      <c r="H11" s="13"/>
       <c r="I11" s="1" t="s">
         <v>51</v>
       </c>
@@ -1176,22 +1176,22 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="10"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C12" s="4">
         <v>0</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
       <c r="F12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
-      <c r="H12" s="10"/>
+      <c r="H12" s="13"/>
       <c r="I12" s="1" t="s">
         <v>52</v>
       </c>
@@ -1203,22 +1203,22 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="10"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="4">
         <v>0</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
       <c r="F13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
       </c>
-      <c r="H13" s="10"/>
+      <c r="H13" s="13"/>
       <c r="I13" s="1" t="s">
         <v>53</v>
       </c>
@@ -1230,22 +1230,22 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="27.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="10"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="4">
         <v>0</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
       <c r="F14" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="H14" s="10"/>
+      <c r="H14" s="13"/>
       <c r="I14" s="1" t="s">
         <v>54</v>
       </c>
@@ -1257,22 +1257,22 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="27.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="11"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
       <c r="G15" s="4">
         <v>0</v>
       </c>
-      <c r="H15" s="11"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="3" t="s">
         <v>63</v>
       </c>
@@ -1284,28 +1284,28 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="27.85" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="7"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="6">
         <f>AVERAGE(C2:C15)</f>
-        <v>0.21428571428571427</v>
-      </c>
-      <c r="D16" s="8" t="s">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
       <c r="G16" s="6">
         <f>AVERAGE(G2:G15)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
       <c r="K16" s="6">
         <f>AVERAGE(K2:K15)</f>
         <v>0</v>

--- a/doc/分工表.xlsx
+++ b/doc/分工表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms169\Desktop\Tuozhu-Software\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD2857A-FE12-4A33-ACFE-FEB611D076CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1CA616-47FF-4B8A-B1FC-4D623C9FED58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{82B2D615-F6D9-4577-86AD-1DF889E5A29C}"/>
   </bookViews>
@@ -1208,7 +1208,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
@@ -1290,7 +1290,7 @@
       <c r="B16" s="10"/>
       <c r="C16" s="6">
         <f>AVERAGE(C2:C15)</f>
-        <v>0.42857142857142855</v>
+        <v>0.5</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>73</v>

--- a/doc/分工表.xlsx
+++ b/doc/分工表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms169\Desktop\Tuozhu-Software\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1CA616-47FF-4B8A-B1FC-4D623C9FED58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762630BE-6518-42B4-B09C-E5C5F6D6EF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{82B2D615-F6D9-4577-86AD-1DF889E5A29C}"/>
   </bookViews>
@@ -976,7 +976,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>24</v>
@@ -1290,7 +1290,7 @@
       <c r="B16" s="10"/>
       <c r="C16" s="6">
         <f>AVERAGE(C2:C15)</f>
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>73</v>
